--- a/inst/apps/EGLEtools/external/RMD/files/OutputFileSubtabs.xlsx
+++ b/inst/apps/EGLEtools/external/RMD/files/OutputFileSubtabs.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tetratechinc-my.sharepoint.com/personal/ben_block_tetratech_com/Documents/GitHub/EGLEtools/inst/apps/EGLEtools/external/RMD/files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="750" documentId="13_ncr:1_{91BD46A0-876E-4F3F-A069-C7C4460D9F1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B9B01A9D-4AC6-4152-9600-4DB5FAAC2A08}"/>
+  <xr:revisionPtr revIDLastSave="866" documentId="13_ncr:1_{91BD46A0-876E-4F3F-A069-C7C4460D9F1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9EDA2D10-57BE-4C8B-8A97-DCF25CC1BB61}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="838" activeTab="5" xr2:uid="{038ACB90-5DA2-4F44-952D-B20E0777567B}"/>
+    <workbookView xWindow="28680" yWindow="-7095" windowWidth="16440" windowHeight="28320" tabRatio="838" activeTab="3" xr2:uid="{038ACB90-5DA2-4F44-952D-B20E0777567B}"/>
   </bookViews>
   <sheets>
     <sheet name="FileBuild_TTAA" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
     <sheet name="South_Classes" sheetId="17" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">FileBuild_About!$A$1:$E$42</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">FileBuild_About!$A$1:$E$36</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="372" uniqueCount="193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="189">
   <si>
     <t>Description</t>
   </si>
@@ -242,9 +242,6 @@
     <t>Richness</t>
   </si>
   <si>
-    <t>100*(8 - X)/(7)</t>
-  </si>
-  <si>
     <t>VeryNarrow</t>
   </si>
   <si>
@@ -254,282 +251,69 @@
     <t>Number of taxa in Orders Ephemeroptera, Plecoptera, and Trichoptera</t>
   </si>
   <si>
-    <t>100*(X - 2.35)/(12.65)</t>
-  </si>
-  <si>
     <t>East</t>
   </si>
   <si>
-    <t>nt_habit_cling</t>
-  </si>
-  <si>
-    <t>Number of taxa of Habit - clingers</t>
-  </si>
-  <si>
     <t>Habit</t>
   </si>
   <si>
-    <t>100*(X - 2)/(10.6)</t>
-  </si>
-  <si>
     <t>nt_NonIns</t>
   </si>
   <si>
     <t>Number of taxa not of Class Insecta</t>
   </si>
   <si>
-    <t>100*(13 - X)/(9)</t>
-  </si>
-  <si>
-    <t>nt_Trich</t>
-  </si>
-  <si>
-    <t>Number of taxa of Order Tricoptera</t>
-  </si>
-  <si>
-    <t>100*(X)/(7)</t>
-  </si>
-  <si>
     <t>WestSteep</t>
   </si>
   <si>
-    <t>nt_tv_toler</t>
-  </si>
-  <si>
-    <t>Number of taxa with tolerance value ≥7 - tolerant</t>
-  </si>
-  <si>
     <t>Tolerance</t>
   </si>
   <si>
-    <t>100*(5 - X)/(5)</t>
-  </si>
-  <si>
-    <t>pi_Cru</t>
-  </si>
-  <si>
-    <t>Percent individuals of Subphylum Crustacea</t>
-  </si>
-  <si>
     <t>Composition</t>
   </si>
   <si>
-    <t>100*(63.71 - X)/(63.71)</t>
-  </si>
-  <si>
-    <t>pi_CruMol</t>
-  </si>
-  <si>
-    <t>Percent individuals of Subphylum Crustacea and Phylum Mollusca</t>
-  </si>
-  <si>
-    <t>100*(51.48 - X)/(50.91)</t>
-  </si>
-  <si>
     <t>Narrow</t>
   </si>
   <si>
-    <t>pi_EPT</t>
-  </si>
-  <si>
-    <t>Percent individuals of Orders Ephemeroptera, Plecoptera, and Trichoptera</t>
-  </si>
-  <si>
-    <t>100*(X - 14.93)/(57.97)</t>
-  </si>
-  <si>
     <t>WestFlat</t>
   </si>
   <si>
-    <t>100*(X - 0.59)/(60.17)</t>
-  </si>
-  <si>
-    <t>pi_EPTNoBaeHydro</t>
-  </si>
-  <si>
-    <t>Percent individuals of Orders Ephemeroptera, Plecoptera and Trichoptera (EPT) and not Families Baetidae or Hydropsychidae</t>
-  </si>
-  <si>
-    <t>100*(X)/(32.58)</t>
-  </si>
-  <si>
-    <t>pi_ffg_col</t>
-  </si>
-  <si>
-    <t>Percent individuals of Functional Feeding Group - collector-gatherer</t>
-  </si>
-  <si>
-    <t>100*(72.31 - X)/(62.64)</t>
-  </si>
-  <si>
-    <t>100*(77.52 - X)/(72.21)</t>
-  </si>
-  <si>
     <t>pi_ffg_pred</t>
   </si>
   <si>
     <t>Percent individuals of Functional Feeding Group - predator</t>
   </si>
   <si>
-    <t>100*(X - 3.21)/(22.51)</t>
-  </si>
-  <si>
     <t>pi_ffg_scrap</t>
   </si>
   <si>
     <t>Percent individuals of Functional Feeding Group - scraper</t>
   </si>
   <si>
-    <t>100*(50.14 - X)/(48.06)</t>
-  </si>
-  <si>
     <t>pi_ffg_shred</t>
   </si>
   <si>
     <t>Percent individuals of Functional Feeding Group - shredder</t>
   </si>
   <si>
-    <t>100*(42.23 - X)/(40.87)</t>
-  </si>
-  <si>
-    <t>100*(51.34 - X)/(49.46)</t>
-  </si>
-  <si>
-    <t>100*(71.15 - X)/(69.82)</t>
-  </si>
-  <si>
     <t>pi_habit_climb</t>
   </si>
   <si>
     <t>Percent individuals of Habit - climbers</t>
   </si>
   <si>
-    <t>100*(18.45 - X)/(18.07)</t>
-  </si>
-  <si>
-    <t>pi_habit_cling</t>
-  </si>
-  <si>
-    <t>Percent individuals of Habit - clingers</t>
-  </si>
-  <si>
-    <t>100*(X - 18.39)/(61.18)</t>
-  </si>
-  <si>
-    <t>100*(X - 4.27)/(67.89)</t>
-  </si>
-  <si>
-    <t>100*(X - 1.29)/(69.73)</t>
-  </si>
-  <si>
-    <t>pi_habit_sprawl</t>
-  </si>
-  <si>
-    <t>Percent individuals of Habit - sprawlers</t>
-  </si>
-  <si>
-    <t>100*(27.03 - X)/(26.45)</t>
-  </si>
-  <si>
-    <t>pi_IsopGastHiru</t>
-  </si>
-  <si>
-    <t>Percent individuals of Order Isopoda, Class Gastropoda, Subclass Hirudinea</t>
-  </si>
-  <si>
-    <t>100*(38.46 - X)/(38.07)</t>
-  </si>
-  <si>
-    <t>100*(48.6 - X)/(47.86)</t>
-  </si>
-  <si>
-    <t>pi_NonIns</t>
-  </si>
-  <si>
-    <t>Percent individuals not of Class Insecta</t>
-  </si>
-  <si>
-    <t>100*(67.29 - X)/(64)</t>
-  </si>
-  <si>
-    <t>pi_Pleco</t>
-  </si>
-  <si>
-    <t>Percent individuals of Order Plecoptera</t>
-  </si>
-  <si>
-    <t>100*(X)/(6.62)</t>
-  </si>
-  <si>
-    <t>pi_tv_intol</t>
-  </si>
-  <si>
-    <t>Percent individuals with tolerance value ≤3 - intolerant</t>
-  </si>
-  <si>
-    <t>100*(X)/(42.08)</t>
-  </si>
-  <si>
-    <t>pi_tv_toler</t>
-  </si>
-  <si>
-    <t>Percent individuals with tolerance value ≥7 - tolerant</t>
-  </si>
-  <si>
-    <t>100*(18.26 - X)/(18.26)</t>
-  </si>
-  <si>
     <t>pt_NonIns</t>
   </si>
   <si>
     <t>Percent of taxa not of Class Insecta</t>
   </si>
   <si>
-    <t>100*(33.33 - X)/(22.62)</t>
-  </si>
-  <si>
-    <t>100*(34.39 - X)/(26.25)</t>
-  </si>
-  <si>
-    <t>100*(38.89 - X)/(28.18)</t>
-  </si>
-  <si>
-    <t>100*(43.51 - X)/(25.33)</t>
-  </si>
-  <si>
-    <t>100*(50 - X)/(30)</t>
-  </si>
-  <si>
-    <t>pt_tv_intol</t>
-  </si>
-  <si>
-    <t>Percent taxa with tolerance value ≤3 - intolerant</t>
-  </si>
-  <si>
-    <t>100*(X - 7.51)/(37.73)</t>
-  </si>
-  <si>
-    <t>100*(X)/(31.06)</t>
-  </si>
-  <si>
     <t>pt_tv_toler</t>
   </si>
   <si>
     <t>Percent taxa with tolerance value ≥7 - tolerant</t>
   </si>
   <si>
-    <t>100*(17.39 - X)/(17.39)</t>
-  </si>
-  <si>
-    <t>100*(30.04 - X)/(25.71)</t>
-  </si>
-  <si>
-    <t>100*(31.93 - X)/(26.61)</t>
-  </si>
-  <si>
-    <t>100*(30.9 - X)/(30.9)</t>
-  </si>
-  <si>
     <t>P51 IBI Score Threshold</t>
   </si>
   <si>
@@ -611,31 +395,235 @@
     <t>results_EGLE_FileBuilder_Output</t>
   </si>
   <si>
+    <t>List of samples assigned to IBI Stream Classes. Contains interim fields necessary for index classification.</t>
+  </si>
+  <si>
+    <t>East of longitude -83.72</t>
+  </si>
+  <si>
+    <t>&lt; 13 ft wide*</t>
+  </si>
+  <si>
+    <t>13 - 21.27 ft wide*</t>
+  </si>
+  <si>
+    <t>21.27 - 68.367 ft wide* AND &lt;=40.067% Catchment Water or Wetland Land Cover**</t>
+  </si>
+  <si>
+    <t>[&gt; 21.27 ft wide* AND &gt;40.067% Catchment Water or Wetland Land Cover**] OR [&gt; 68.367 ft wide*]</t>
+  </si>
+  <si>
+    <t>West of longitude -83.72 AND % slope &lt; 0.2976*</t>
+  </si>
+  <si>
+    <t>West of longitude -83.72 AND % slope &gt; 0.2976*</t>
+  </si>
+  <si>
+    <t>pi_tv_toler6</t>
+  </si>
+  <si>
+    <t>nt_POET</t>
+  </si>
+  <si>
+    <t>pt_ffg_scrap</t>
+  </si>
+  <si>
+    <t>pt_habit_sprawl</t>
+  </si>
+  <si>
+    <t>pt_POET</t>
+  </si>
+  <si>
+    <t>pt_habit_burrow</t>
+  </si>
+  <si>
+    <t>pt_habit_swim</t>
+  </si>
+  <si>
+    <t>pt_ffg_pred</t>
+  </si>
+  <si>
+    <t>pi_habit_swim</t>
+  </si>
+  <si>
+    <t>pt_ffg_col</t>
+  </si>
+  <si>
+    <t>pt_Insect</t>
+  </si>
+  <si>
+    <t>pt_tv_ntol</t>
+  </si>
+  <si>
+    <t>pt_tv_toler6</t>
+  </si>
+  <si>
+    <t>nt_ffg_pred</t>
+  </si>
+  <si>
+    <t>nt_total</t>
+  </si>
+  <si>
+    <t>pi_OligoHiru</t>
+  </si>
+  <si>
+    <t>100 * (56.3 - metric) / (56.3 - 1.23)</t>
+  </si>
+  <si>
+    <t>100 * (66.54 - metric) / (66.54 - 1.93)</t>
+  </si>
+  <si>
+    <t>100 * (32.98 - metric) / (32.98 - 9.18)</t>
+  </si>
+  <si>
+    <t>100 * (metric - 5.2) / (18 - 5.2)</t>
+  </si>
+  <si>
+    <t>100 * (metric - 4.2) / (24 - 4.2)</t>
+  </si>
+  <si>
+    <t>100 * (metric - 8.77) / (25.88 - 8.77)</t>
+  </si>
+  <si>
+    <t>100 * (10.35 - metric) / (10.35 - 2)</t>
+  </si>
+  <si>
+    <t>100 * (52.68 - metric) / (52.68 - 0.86)</t>
+  </si>
+  <si>
+    <t>100 * (metric - 28.12) / (61.5 - 28.12)</t>
+  </si>
+  <si>
+    <t>100 * (metric - 12.5) / (27.16 - 12.5)</t>
+  </si>
+  <si>
+    <t>100 * (8 - metric) / (8 - 1)</t>
+  </si>
+  <si>
+    <t>100 * (19.48 - metric) / (19.48 - 0)</t>
+  </si>
+  <si>
+    <t>100 * (21.62 - metric) / (21.62 - 6.62)</t>
+  </si>
+  <si>
+    <t>100 * (39.39 - metric) / (39.39 - 3.44)</t>
+  </si>
+  <si>
+    <t>100 * (metric - 7) / (16.2 - 7)</t>
+  </si>
+  <si>
+    <t>100 * (metric - 19.29) / (42.3 - 19.29)</t>
+  </si>
+  <si>
+    <t>100 * (30.01 - metric) / (30.01 - 0.91)</t>
+  </si>
+  <si>
+    <t>100 * (38.41 - metric) / (38.41 - 3.89)</t>
+  </si>
+  <si>
+    <t>100 * (metric - 31.97) / (58.18 - 31.97)</t>
+  </si>
+  <si>
+    <t>100 * (metric - 3.56) / (31.95 - 3.56)</t>
+  </si>
+  <si>
+    <t>100 * (metric - 3.02) / (35.81 - 3.02)</t>
+  </si>
+  <si>
+    <t>100 * (44.9 - metric) / (44.9 - 17.81)</t>
+  </si>
+  <si>
+    <t>100 * (27.78 - metric) / (27.78 - 5.8)</t>
+  </si>
+  <si>
+    <t>100 * (metric - 1.55) / (10 - 1.55)</t>
+  </si>
+  <si>
+    <t>100 * (metric - 55.56) / (82.61 - 55.56)</t>
+  </si>
+  <si>
+    <t>100 * (metric - 36.99) / (76.47 - 36.99)</t>
+  </si>
+  <si>
+    <t>100 * (58.65 - metric) / (58.65 - 21)</t>
+  </si>
+  <si>
+    <t>100 * (metric - 52.22) / (84.77 - 52.22)</t>
+  </si>
+  <si>
+    <t>100 * (metric - 4) / (12 - 4)</t>
+  </si>
+  <si>
+    <t>100 * (metric - 17) / (35 - 17)</t>
+  </si>
+  <si>
+    <t>100 * (60 - metric) / (60 - 27.18)</t>
+  </si>
+  <si>
+    <t>100 * (35.38 - metric) / (35.38 - 0.31)</t>
+  </si>
+  <si>
+    <t>100 * (42.86 - metric) / (42.86 - 18.18)</t>
+  </si>
+  <si>
+    <t>100 * (metric - 50) / (82.19 - 50)</t>
+  </si>
+  <si>
+    <t>100 * (metric - 2) / (12 - 2)</t>
+  </si>
+  <si>
+    <t>Relative Richness</t>
+  </si>
+  <si>
+    <t>Percent individuals of Habit - swimmers</t>
+  </si>
+  <si>
+    <t>Number of taxa of Functional Feeding Group - predator</t>
+  </si>
+  <si>
+    <t>Number of total taxa</t>
+  </si>
+  <si>
+    <t>Percent of individuals with tolerance value &gt; 6 - tolerant</t>
+  </si>
+  <si>
+    <t>Percent of taxa of Functional Feeding Group - predator</t>
+  </si>
+  <si>
+    <t>Percent of taxa of Functional Feeding Group - collector-gatherer</t>
+  </si>
+  <si>
+    <t>Number of taxa in Orders Plecoptera, Odonanta, Ephemeroptera, and Trichoptera</t>
+  </si>
+  <si>
+    <t>Percent of individuals in Class/SubClass Oligochaeta or SubClass Hirudinea</t>
+  </si>
+  <si>
+    <t>Percent of taxa in Orders Plecoptera, Odonanta, Ephemeroptera, and Trichoptera</t>
+  </si>
+  <si>
+    <t>Percent of taxa with tolerance value &gt; 6 - tolerant</t>
+  </si>
+  <si>
+    <t>Percent of taxa with tolerance value &lt; 6 - intolerant</t>
+  </si>
+  <si>
+    <t>Percent of taxa of Functional Feeding Group - scraper</t>
+  </si>
+  <si>
+    <t>Percent of taxa of Habit - burrowers</t>
+  </si>
+  <si>
+    <t>Percent of taxa of Habit - sprawlers</t>
+  </si>
+  <si>
+    <t>Percent of taxa of Habit - swimmers</t>
+  </si>
+  <si>
+    <t>Percent of taxa of Class Insecta</t>
+  </si>
+  <si>
     <t>WideOrMidSizeWet</t>
-  </si>
-  <si>
-    <t>List of samples assigned to IBI Stream Classes. Contains interim fields necessary for index classification.</t>
-  </si>
-  <si>
-    <t>East of longitude -83.72</t>
-  </si>
-  <si>
-    <t>&lt; 13 ft wide*</t>
-  </si>
-  <si>
-    <t>13 - 21.27 ft wide*</t>
-  </si>
-  <si>
-    <t>21.27 - 68.367 ft wide* AND &lt;=40.067% Catchment Water or Wetland Land Cover**</t>
-  </si>
-  <si>
-    <t>[&gt; 21.27 ft wide* AND &gt;40.067% Catchment Water or Wetland Land Cover**] OR [&gt; 68.367 ft wide*]</t>
-  </si>
-  <si>
-    <t>West of longitude -83.72 AND % slope &lt; 0.2976*</t>
-  </si>
-  <si>
-    <t>West of longitude -83.72 AND % slope &gt; 0.2976*</t>
   </si>
 </sst>
 </file>
@@ -1054,12 +1042,12 @@
         <v>21</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>161</v>
+        <v>89</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>176</v>
+        <v>104</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>22</v>
@@ -1070,35 +1058,35 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>177</v>
+        <v>105</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>22</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>162</v>
+        <v>90</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>174</v>
+        <v>102</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>22</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>163</v>
+        <v>91</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>175</v>
+        <v>103</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>22</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>164</v>
+        <v>92</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="75" x14ac:dyDescent="0.25">
@@ -1106,10 +1094,10 @@
         <v>43</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>160</v>
+        <v>88</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>165</v>
+        <v>93</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="30" x14ac:dyDescent="0.25">
@@ -1117,10 +1105,10 @@
         <v>44</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>160</v>
+        <v>88</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>166</v>
+        <v>94</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="30" x14ac:dyDescent="0.25">
@@ -1128,32 +1116,32 @@
         <v>45</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>160</v>
+        <v>88</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>167</v>
+        <v>95</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>172</v>
+        <v>100</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>160</v>
+        <v>88</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>185</v>
+        <v>112</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>158</v>
+        <v>86</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>183</v>
+        <v>111</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>159</v>
+        <v>87</v>
       </c>
     </row>
   </sheetData>
@@ -1222,7 +1210,7 @@
         <v>10</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>173</v>
+        <v>101</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -1392,7 +1380,7 @@
         <v>14</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>178</v>
+        <v>106</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
@@ -1464,7 +1452,7 @@
         <v>21</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>161</v>
+        <v>89</v>
       </c>
     </row>
     <row r="3" spans="1:3" s="1" customFormat="1" ht="30" x14ac:dyDescent="0.25">
@@ -1494,7 +1482,7 @@
         <v>52</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>160</v>
+        <v>88</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>53</v>
@@ -1505,10 +1493,10 @@
         <v>40</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>160</v>
+        <v>88</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>168</v>
+        <v>96</v>
       </c>
     </row>
     <row r="7" spans="1:3" s="1" customFormat="1" ht="45" x14ac:dyDescent="0.25">
@@ -1516,10 +1504,10 @@
         <v>41</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>160</v>
+        <v>88</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>180</v>
+        <v>108</v>
       </c>
     </row>
     <row r="8" spans="1:3" s="1" customFormat="1" ht="45" x14ac:dyDescent="0.25">
@@ -1527,21 +1515,21 @@
         <v>42</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>160</v>
+        <v>88</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>181</v>
+        <v>109</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>169</v>
+        <v>97</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>182</v>
+        <v>110</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>179</v>
+        <v>107</v>
       </c>
     </row>
   </sheetData>
@@ -1551,19 +1539,19 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4C0A9FE-C8CE-4A36-85A6-2441939240FA}">
-  <dimension ref="A1:E42"/>
+  <dimension ref="A1:E36"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.5703125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="18.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="44.42578125" customWidth="1"/>
+    <col min="3" max="3" width="83.28515625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12.28515625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="20.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>171</v>
+        <v>99</v>
       </c>
       <c r="B1" t="s">
         <v>54</v>
@@ -1580,104 +1568,104 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B2" t="s">
-        <v>67</v>
+        <v>133</v>
       </c>
       <c r="C2" t="s">
-        <v>68</v>
+        <v>173</v>
       </c>
       <c r="D2" t="s">
-        <v>69</v>
+        <v>34</v>
       </c>
       <c r="E2" t="s">
-        <v>70</v>
+        <v>170</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B3" t="s">
-        <v>74</v>
+        <v>135</v>
       </c>
       <c r="C3" t="s">
-        <v>75</v>
+        <v>179</v>
       </c>
       <c r="D3" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="E3" t="s">
-        <v>76</v>
+        <v>167</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B4" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="C4" t="s">
-        <v>125</v>
+        <v>177</v>
       </c>
       <c r="D4" t="s">
-        <v>84</v>
+        <v>34</v>
       </c>
       <c r="E4" t="s">
-        <v>127</v>
+        <v>168</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B5" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="C5" t="s">
-        <v>135</v>
+        <v>187</v>
       </c>
       <c r="D5" t="s">
-        <v>80</v>
+        <v>171</v>
       </c>
       <c r="E5" t="s">
-        <v>136</v>
+        <v>169</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B6" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="C6" t="s">
-        <v>141</v>
+        <v>181</v>
       </c>
       <c r="D6" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="E6" t="s">
-        <v>146</v>
+        <v>166</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="B7" t="s">
-        <v>151</v>
+        <v>58</v>
       </c>
       <c r="C7" t="s">
-        <v>152</v>
+        <v>59</v>
       </c>
       <c r="D7" t="s">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="E7" t="s">
-        <v>155</v>
+        <v>146</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -1685,16 +1673,16 @@
         <v>57</v>
       </c>
       <c r="B8" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="C8" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="D8" t="s">
         <v>60</v>
       </c>
       <c r="E8" t="s">
-        <v>61</v>
+        <v>150</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -1702,16 +1690,16 @@
         <v>57</v>
       </c>
       <c r="B9" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C9" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="D9" t="s">
-        <v>80</v>
+        <v>34</v>
       </c>
       <c r="E9" t="s">
-        <v>81</v>
+        <v>149</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
@@ -1719,16 +1707,16 @@
         <v>57</v>
       </c>
       <c r="B10" t="s">
-        <v>86</v>
+        <v>127</v>
       </c>
       <c r="C10" t="s">
-        <v>87</v>
+        <v>176</v>
       </c>
       <c r="D10" t="s">
-        <v>84</v>
+        <v>34</v>
       </c>
       <c r="E10" t="s">
-        <v>88</v>
+        <v>151</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
@@ -1736,16 +1724,16 @@
         <v>57</v>
       </c>
       <c r="B11" t="s">
-        <v>102</v>
+        <v>126</v>
       </c>
       <c r="C11" t="s">
-        <v>103</v>
+        <v>186</v>
       </c>
       <c r="D11" t="s">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="E11" t="s">
-        <v>104</v>
+        <v>148</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
@@ -1753,532 +1741,430 @@
         <v>57</v>
       </c>
       <c r="B12" t="s">
-        <v>108</v>
+        <v>83</v>
       </c>
       <c r="C12" t="s">
-        <v>109</v>
+        <v>84</v>
       </c>
       <c r="D12" t="s">
-        <v>34</v>
+        <v>69</v>
       </c>
       <c r="E12" t="s">
-        <v>110</v>
+        <v>147</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>57</v>
+        <v>71</v>
       </c>
       <c r="B13" t="s">
-        <v>116</v>
+        <v>66</v>
       </c>
       <c r="C13" t="s">
-        <v>117</v>
+        <v>67</v>
       </c>
       <c r="D13" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="E13" t="s">
-        <v>118</v>
+        <v>142</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>57</v>
+        <v>71</v>
       </c>
       <c r="B14" t="s">
-        <v>140</v>
+        <v>77</v>
       </c>
       <c r="C14" t="s">
-        <v>141</v>
+        <v>78</v>
       </c>
       <c r="D14" t="s">
-        <v>60</v>
+        <v>34</v>
       </c>
       <c r="E14" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>89</v>
+        <v>71</v>
       </c>
       <c r="B15" t="s">
-        <v>90</v>
+        <v>125</v>
       </c>
       <c r="C15" t="s">
-        <v>91</v>
+        <v>184</v>
       </c>
       <c r="D15" t="s">
-        <v>84</v>
+        <v>65</v>
       </c>
       <c r="E15" t="s">
-        <v>92</v>
+        <v>145</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>89</v>
+        <v>71</v>
       </c>
       <c r="B16" t="s">
-        <v>108</v>
+        <v>124</v>
       </c>
       <c r="C16" t="s">
-        <v>109</v>
+        <v>180</v>
       </c>
       <c r="D16" t="s">
-        <v>34</v>
+        <v>171</v>
       </c>
       <c r="E16" t="s">
-        <v>111</v>
+        <v>144</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>89</v>
+        <v>61</v>
       </c>
       <c r="B17" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="C17" t="s">
-        <v>114</v>
+        <v>178</v>
       </c>
       <c r="D17" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="E17" t="s">
-        <v>115</v>
+        <v>139</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>89</v>
+        <v>61</v>
       </c>
       <c r="B18" t="s">
-        <v>137</v>
+        <v>77</v>
       </c>
       <c r="C18" t="s">
-        <v>138</v>
+        <v>78</v>
       </c>
       <c r="D18" t="s">
-        <v>80</v>
+        <v>34</v>
       </c>
       <c r="E18" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>89</v>
+        <v>61</v>
       </c>
       <c r="B19" t="s">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="C19" t="s">
-        <v>141</v>
+        <v>175</v>
       </c>
       <c r="D19" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="E19" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B20" t="s">
-        <v>63</v>
+        <v>122</v>
       </c>
       <c r="C20" t="s">
-        <v>64</v>
+        <v>183</v>
       </c>
       <c r="D20" t="s">
-        <v>60</v>
+        <v>34</v>
       </c>
       <c r="E20" t="s">
-        <v>65</v>
+        <v>140</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B21" t="s">
-        <v>82</v>
+        <v>123</v>
       </c>
       <c r="C21" t="s">
-        <v>83</v>
+        <v>185</v>
       </c>
       <c r="D21" t="s">
-        <v>84</v>
+        <v>65</v>
       </c>
       <c r="E21" t="s">
-        <v>85</v>
+        <v>141</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B22" t="s">
-        <v>108</v>
+        <v>81</v>
       </c>
       <c r="C22" t="s">
-        <v>109</v>
+        <v>82</v>
       </c>
       <c r="D22" t="s">
-        <v>34</v>
+        <v>171</v>
       </c>
       <c r="E22" t="s">
-        <v>112</v>
+        <v>138</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="B23" t="s">
-        <v>116</v>
+        <v>133</v>
       </c>
       <c r="C23" t="s">
-        <v>117</v>
+        <v>173</v>
       </c>
       <c r="D23" t="s">
-        <v>69</v>
+        <v>34</v>
       </c>
       <c r="E23" t="s">
-        <v>119</v>
+        <v>164</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="B24" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="C24" t="s">
-        <v>141</v>
+        <v>174</v>
       </c>
       <c r="D24" t="s">
         <v>60</v>
       </c>
       <c r="E24" t="s">
-        <v>144</v>
+        <v>165</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="B25" t="s">
-        <v>147</v>
+        <v>130</v>
       </c>
       <c r="C25" t="s">
-        <v>148</v>
+        <v>187</v>
       </c>
       <c r="D25" t="s">
-        <v>80</v>
+        <v>171</v>
       </c>
       <c r="E25" t="s">
-        <v>149</v>
+        <v>163</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>93</v>
+        <v>72</v>
       </c>
       <c r="B26" t="s">
-        <v>90</v>
+        <v>132</v>
       </c>
       <c r="C26" t="s">
-        <v>91</v>
+        <v>181</v>
       </c>
       <c r="D26" t="s">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="E26" t="s">
-        <v>94</v>
+        <v>162</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>93</v>
+        <v>68</v>
       </c>
       <c r="B27" t="s">
-        <v>98</v>
+        <v>62</v>
       </c>
       <c r="C27" t="s">
-        <v>99</v>
+        <v>63</v>
       </c>
       <c r="D27" t="s">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="E27" t="s">
-        <v>100</v>
+        <v>159</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>93</v>
+        <v>68</v>
       </c>
       <c r="B28" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="C28" t="s">
-        <v>122</v>
+        <v>177</v>
       </c>
       <c r="D28" t="s">
-        <v>69</v>
+        <v>34</v>
       </c>
       <c r="E28" t="s">
-        <v>123</v>
+        <v>157</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>93</v>
+        <v>68</v>
       </c>
       <c r="B29" t="s">
-        <v>140</v>
+        <v>126</v>
       </c>
       <c r="C29" t="s">
-        <v>141</v>
+        <v>186</v>
       </c>
       <c r="D29" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="E29" t="s">
-        <v>145</v>
+        <v>158</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>93</v>
+        <v>68</v>
       </c>
       <c r="B30" t="s">
-        <v>147</v>
+        <v>130</v>
       </c>
       <c r="C30" t="s">
-        <v>148</v>
+        <v>187</v>
       </c>
       <c r="D30" t="s">
-        <v>80</v>
+        <v>171</v>
       </c>
       <c r="E30" t="s">
-        <v>150</v>
+        <v>160</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>93</v>
+        <v>68</v>
       </c>
       <c r="B31" t="s">
-        <v>151</v>
+        <v>131</v>
       </c>
       <c r="C31" t="s">
-        <v>152</v>
+        <v>182</v>
       </c>
       <c r="D31" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="E31" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>77</v>
+        <v>188</v>
       </c>
       <c r="B32" t="s">
+        <v>73</v>
+      </c>
+      <c r="C32" t="s">
         <v>74</v>
       </c>
-      <c r="C32" t="s">
-        <v>75</v>
-      </c>
       <c r="D32" t="s">
-        <v>60</v>
+        <v>34</v>
       </c>
       <c r="E32" t="s">
-        <v>76</v>
+        <v>155</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>77</v>
+        <v>188</v>
       </c>
       <c r="B33" t="s">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="C33" t="s">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="D33" t="s">
-        <v>84</v>
+        <v>34</v>
       </c>
       <c r="E33" t="s">
-        <v>97</v>
+        <v>153</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>77</v>
+        <v>188</v>
       </c>
       <c r="B34" t="s">
-        <v>98</v>
+        <v>79</v>
       </c>
       <c r="C34" t="s">
-        <v>99</v>
+        <v>80</v>
       </c>
       <c r="D34" t="s">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="E34" t="s">
-        <v>101</v>
+        <v>152</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>77</v>
+        <v>188</v>
       </c>
       <c r="B35" t="s">
-        <v>116</v>
+        <v>128</v>
       </c>
       <c r="C35" t="s">
-        <v>117</v>
+        <v>172</v>
       </c>
       <c r="D35" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E35" t="s">
-        <v>120</v>
+        <v>156</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>77</v>
+        <v>188</v>
       </c>
       <c r="B36" t="s">
-        <v>151</v>
+        <v>124</v>
       </c>
       <c r="C36" t="s">
-        <v>152</v>
+        <v>180</v>
       </c>
       <c r="D36" t="s">
-        <v>80</v>
+        <v>171</v>
       </c>
       <c r="E36" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>184</v>
-      </c>
-      <c r="B37" t="s">
-        <v>71</v>
-      </c>
-      <c r="C37" t="s">
-        <v>72</v>
-      </c>
-      <c r="D37" t="s">
-        <v>60</v>
-      </c>
-      <c r="E37" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>184</v>
-      </c>
-      <c r="B38" t="s">
-        <v>105</v>
-      </c>
-      <c r="C38" t="s">
-        <v>106</v>
-      </c>
-      <c r="D38" t="s">
-        <v>34</v>
-      </c>
-      <c r="E38" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>184</v>
-      </c>
-      <c r="B39" t="s">
-        <v>124</v>
-      </c>
-      <c r="C39" t="s">
-        <v>125</v>
-      </c>
-      <c r="D39" t="s">
-        <v>84</v>
-      </c>
-      <c r="E39" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>184</v>
-      </c>
-      <c r="B40" t="s">
-        <v>128</v>
-      </c>
-      <c r="C40" t="s">
-        <v>129</v>
-      </c>
-      <c r="D40" t="s">
-        <v>84</v>
-      </c>
-      <c r="E40" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>184</v>
-      </c>
-      <c r="B41" t="s">
-        <v>131</v>
-      </c>
-      <c r="C41" t="s">
-        <v>132</v>
-      </c>
-      <c r="D41" t="s">
-        <v>84</v>
-      </c>
-      <c r="E41" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>184</v>
-      </c>
-      <c r="B42" t="s">
-        <v>151</v>
-      </c>
-      <c r="C42" t="s">
-        <v>152</v>
-      </c>
-      <c r="D42" t="s">
-        <v>80</v>
-      </c>
-      <c r="E42" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E42" xr:uid="{D4C0A9FE-C8CE-4A36-85A6-2441939240FA}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E42">
-      <sortCondition ref="A1:A42"/>
+  <autoFilter ref="A1:E36" xr:uid="{D4C0A9FE-C8CE-4A36-85A6-2441939240FA}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E36">
+      <sortCondition ref="A1:A36"/>
     </sortState>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2296,15 +2182,15 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>171</v>
+        <v>99</v>
       </c>
       <c r="B1" t="s">
-        <v>157</v>
+        <v>85</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B2">
         <v>59</v>
@@ -2312,7 +2198,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>89</v>
+        <v>71</v>
       </c>
       <c r="B3">
         <v>48</v>
@@ -2328,7 +2214,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>170</v>
+        <v>98</v>
       </c>
       <c r="B5">
         <v>45</v>
@@ -2336,7 +2222,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>93</v>
+        <v>72</v>
       </c>
       <c r="B6">
         <v>46</v>
@@ -2344,7 +2230,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="B7">
         <v>42</v>
@@ -2352,7 +2238,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B8">
         <v>46</v>
@@ -2374,7 +2260,7 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>171</v>
+        <v>99</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>0</v>
@@ -2382,18 +2268,18 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>187</v>
+        <v>114</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>89</v>
+        <v>71</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>188</v>
+        <v>115</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="30" x14ac:dyDescent="0.25">
@@ -2401,15 +2287,15 @@
         <v>57</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>189</v>
+        <v>116</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>170</v>
+        <v>98</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>190</v>
+        <v>117</v>
       </c>
     </row>
   </sheetData>
@@ -2429,7 +2315,7 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>171</v>
+        <v>99</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>0</v>
@@ -2437,26 +2323,26 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>93</v>
+        <v>72</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>191</v>
+        <v>118</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>192</v>
+        <v>119</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>186</v>
+        <v>113</v>
       </c>
     </row>
   </sheetData>

--- a/inst/apps/EGLEtools/external/RMD/files/OutputFileSubtabs.xlsx
+++ b/inst/apps/EGLEtools/external/RMD/files/OutputFileSubtabs.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tetratechinc-my.sharepoint.com/personal/ben_block_tetratech_com/Documents/GitHub/EGLEtools/inst/apps/EGLEtools/external/RMD/files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="866" documentId="13_ncr:1_{91BD46A0-876E-4F3F-A069-C7C4460D9F1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9EDA2D10-57BE-4C8B-8A97-DCF25CC1BB61}"/>
+  <xr:revisionPtr revIDLastSave="873" documentId="13_ncr:1_{91BD46A0-876E-4F3F-A069-C7C4460D9F1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BBC6A9B6-CA7B-44BE-9377-A7AC9028FB6F}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-7095" windowWidth="16440" windowHeight="28320" tabRatio="838" activeTab="3" xr2:uid="{038ACB90-5DA2-4F44-952D-B20E0777567B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="838" activeTab="4" xr2:uid="{038ACB90-5DA2-4F44-952D-B20E0777567B}"/>
   </bookViews>
   <sheets>
     <sheet name="FileBuild_TTAA" sheetId="1" r:id="rId1"/>
@@ -2193,7 +2193,7 @@
         <v>61</v>
       </c>
       <c r="B2">
-        <v>59</v>
+        <v>40</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -2201,7 +2201,7 @@
         <v>71</v>
       </c>
       <c r="B3">
-        <v>48</v>
+        <v>44</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -2209,7 +2209,7 @@
         <v>57</v>
       </c>
       <c r="B4">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -2217,7 +2217,7 @@
         <v>98</v>
       </c>
       <c r="B5">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -2225,7 +2225,7 @@
         <v>72</v>
       </c>
       <c r="B6">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -2233,7 +2233,7 @@
         <v>68</v>
       </c>
       <c r="B7">
-        <v>42</v>
+        <v>50</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -2241,7 +2241,7 @@
         <v>64</v>
       </c>
       <c r="B8">
-        <v>46</v>
+        <v>68</v>
       </c>
     </row>
   </sheetData>
